--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122734725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105350</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562772</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626148</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,108 +797,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>122734725</v>
-      </c>
-      <c r="B3" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>562772</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6626148</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122734725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562772</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626148</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122734725</v>
       </c>
       <c r="B3" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122734725</v>
+        <v>116380784</v>
       </c>
       <c r="B3" t="n">
-        <v>105502</v>
+        <v>96709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
+          <t>Sellbergsängen N, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562772</v>
+        <v>562828</v>
       </c>
       <c r="R3" t="n">
-        <v>6626148</v>
+        <v>6625924</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,21 +884,129 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hällmark i ung barrblandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122734725</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105502</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562772</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626148</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Bertil Svensson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Bertil Svensson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116380767</v>
+        <v>122734725</v>
       </c>
       <c r="B2" t="n">
-        <v>96721</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sellbergsängen N, Vstm</t>
+          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562828</v>
+        <v>562772</v>
       </c>
       <c r="R2" t="n">
-        <v>6625924</v>
+        <v>6626148</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,39 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hällmark i ung barrblandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116380784</v>
+        <v>116380767</v>
       </c>
       <c r="B3" t="n">
-        <v>96709</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +783,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -878,6 +857,11 @@
           <t>2024-04-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122734725</v>
+        <v>116380784</v>
       </c>
       <c r="B4" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,37 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sellbergsängen, Sellbergsängen, Vstm</t>
+          <t>Sellbergsängen N, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562772</v>
+        <v>562828</v>
       </c>
       <c r="R4" t="n">
-        <v>6626148</v>
+        <v>6625924</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,18 +971,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hällmark i ung barrblandskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 4082-2025 artfynd.xlsx
+++ b/artfynd/A 4082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122734725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116380767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,8 +1007,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116380784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>